--- a/artfynd/A 5221-2025 artfynd.xlsx
+++ b/artfynd/A 5221-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AY53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,56 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>57147755</v>
+        <v>67081796</v>
       </c>
       <c r="B2" t="n">
-        <v>96252</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223591</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skorvdalen, Hjd</t>
+          <t>Kvarnsjö, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>449072.3017792593</v>
+        <v>448908</v>
       </c>
       <c r="R2" t="n">
-        <v>6919617.551932113</v>
+        <v>6919288</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-07-29</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-07-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Fynd från Forskningsresan i naturvårdens utmarker 2015.</t>
+          <t>2015-07-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,27 +760,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>57147814</v>
+        <v>67081811</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,39 +787,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skorvdalen, Hjd</t>
+          <t>Kvarnsjö, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>449072.3017792593</v>
+        <v>449217</v>
       </c>
       <c r="R3" t="n">
-        <v>6919617.551932113</v>
+        <v>6919807</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,27 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2015-07-29</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2015-07-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På Gran. Fynd från Forskningsresan i naturvårdens utmarker 2015.</t>
+          <t>2015-07-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,67 +861,64 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>57055851</v>
+        <v>67081825</v>
       </c>
       <c r="B4" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6464</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skorvdalen, Hjd</t>
+          <t>Kvarnsjö, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>449041.5515921504</v>
+        <v>449419</v>
       </c>
       <c r="R4" t="n">
-        <v>6919367.169527217</v>
+        <v>6919732</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,27 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2015-07-29</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2015-07-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På Sälg 30 cm. Fynd från Forskningsresan i naturvårdens utmarker 2015.</t>
+          <t>2015-07-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,27 +962,26 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>57147926</v>
+        <v>81530</v>
       </c>
       <c r="B5" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1049,39 +989,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>skorvdalen, Hjd</t>
+          <t>Skorvdalen, Vemdalen,, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>449072.6938274027</v>
+        <v>449323</v>
       </c>
       <c r="R5" t="n">
-        <v>6919490.963470953</v>
+        <v>6919358</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,27 +1044,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2015-07-29</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-07-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2015-07-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-07-26</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Fynd från Forskningsresan i naturvårdens utmarker 2015.</t>
+          <t>området mellan Rönningsvallen - Gammelnipan - Nipfjället - Gråberget,</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,27 +1069,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>malin almquist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Lars-Olof Grund</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Lst Z Artdatabas</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>57147518</v>
+        <v>279930</v>
       </c>
       <c r="B6" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,21 +1096,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>864</v>
+        <v>308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1190,14 +1118,14 @@
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skorvdalen, Hjd</t>
+          <t>Skorvdalen, Vemdalen,, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>449072.3017792593</v>
+        <v>449484</v>
       </c>
       <c r="R6" t="n">
-        <v>6919617.551932113</v>
+        <v>6919997</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,27 +1152,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2015-07-29</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-07-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2015-07-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-07-26</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På Granlåga (3 st).  Fynd från Forskningsresan i naturvårdens utmarker 2015.</t>
+          <t>området mellan Rönningsvallen - Gammelnipan - Nipfjället - Gråberget,</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,64 +1177,62 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>malin almquist</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Lars-Olof Grund</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Lst Z Artdatabas</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>57055860</v>
+        <v>104888</v>
       </c>
       <c r="B7" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83302</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229497</v>
+        <v>310</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skorvdalen, Hjd</t>
+          <t>Skorvdalen, Vemdalen,, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>449041.5515921504</v>
+        <v>448546</v>
       </c>
       <c r="R7" t="n">
-        <v>6919367.169527217</v>
+        <v>6919610</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1343,27 +1259,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2015-07-29</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-07-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2015-07-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-07-26</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På Sälg 30 cm.  Fynd från Forskningsresan i naturvårdens utmarker 2015.</t>
+          <t>området mellan Rönningsvallen - Gammelnipan - Nipfjället - Gråberget,</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1378,67 +1284,64 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>malin almquist</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Lars-Olof Grund</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Lst Z Artdatabas</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>57147786</v>
+        <v>67081810</v>
       </c>
       <c r="B8" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skorvdalen, Hjd</t>
+          <t>Kvarnsjö, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>449072.3017792593</v>
+        <v>449175</v>
       </c>
       <c r="R8" t="n">
-        <v>6919617.551932113</v>
+        <v>6919771</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1462,27 +1365,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2015-07-29</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2015-07-29</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På Sälg levande. Fynd från Forskningsresan i naturvårdens utmarker 2015.</t>
+          <t>2015-07-17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,27 +1385,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>62064253</v>
+        <v>67081815</v>
       </c>
       <c r="B9" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1525,37 +1412,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1204</v>
+        <v>510</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skorvdalen Vemdalen, Hjd</t>
+          <t>Kvarnsjö, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>448900.3828601408</v>
+        <v>449252</v>
       </c>
       <c r="R9" t="n">
-        <v>6918911.62391693</v>
+        <v>6919861</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1579,27 +1466,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2007-07-26</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2007-07-26</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Naturinventering av Skorvdalen / Lars-Olof Grund 2007. Skorvdalen, området mellan Rönningsvallen - Gammelnipan - Nipfjället - Gråberget,</t>
+          <t>2015-07-17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1614,71 +1486,64 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lars-Olof Grund</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>Lst Z Artdatabas</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2090122</v>
+        <v>67081820</v>
       </c>
       <c r="B10" t="n">
-        <v>73691</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6486</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skorvdalen, Vemdalen,, Hjd</t>
+          <t>Kvarnsjö, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>448946.9176390536</v>
+        <v>449561</v>
       </c>
       <c r="R10" t="n">
-        <v>6918948.01338965</v>
+        <v>6920045</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1702,27 +1567,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2007-07-26</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2007-07-26</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>området mellan Rönningsvallen - Gammelnipan - Nipfjället - Gråberget,</t>
+          <t>2015-07-17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1737,31 +1587,26 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>malin almquist</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lars-Olof Grund</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>Lst Z Artdatabas</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>811799</v>
+        <v>67081827</v>
       </c>
       <c r="B11" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1769,39 +1614,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skorvdalen, Vemdalen,, Hjd</t>
+          <t>Kvarnsjö, Hjd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>448545.6272013072</v>
+        <v>449112</v>
       </c>
       <c r="R11" t="n">
-        <v>6919609.857464722</v>
+        <v>6919301</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1825,27 +1668,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2007-07-26</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2007-07-26</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>området mellan Rönningsvallen - Gammelnipan - Nipfjället - Gråberget,</t>
+          <t>2015-07-17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1860,31 +1688,26 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>malin almquist</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lars-Olof Grund</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>Lst Z Artdatabas</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>316141</v>
+        <v>316127</v>
       </c>
       <c r="B12" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1910,6 +1733,7 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1917,10 +1741,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>449539.94145545</v>
+        <v>449031</v>
       </c>
       <c r="R12" t="n">
-        <v>6920205.281648007</v>
+        <v>6919370</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1950,19 +1774,9 @@
           <t>2007-07-26</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2007-07-26</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1998,15 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>316139</v>
+        <v>316130</v>
       </c>
       <c r="B13" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,10 +1849,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>449288.3717865782</v>
+        <v>448611</v>
       </c>
       <c r="R13" t="n">
-        <v>6919750.11558143</v>
+        <v>6919440</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2073,19 +1882,9 @@
           <t>2007-07-26</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2007-07-26</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2121,15 +1920,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>81530</v>
+        <v>316133</v>
       </c>
       <c r="B14" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2137,24 +1931,25 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2162,10 +1957,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>449323.2806950421</v>
+        <v>448502</v>
       </c>
       <c r="R14" t="n">
-        <v>6919357.783861226</v>
+        <v>6919601</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2195,19 +1990,9 @@
           <t>2007-07-26</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2007-07-26</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2243,15 +2028,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>316127</v>
+        <v>316139</v>
       </c>
       <c r="B15" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2285,10 +2065,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>449031.3802862529</v>
+        <v>449288</v>
       </c>
       <c r="R15" t="n">
-        <v>6919370.106861067</v>
+        <v>6919750</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2318,19 +2098,9 @@
           <t>2007-07-26</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2007-07-26</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2369,12 +2139,7 @@
         <v>316140</v>
       </c>
       <c r="B16" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2408,10 +2173,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>449547.0352188181</v>
+        <v>449547</v>
       </c>
       <c r="R16" t="n">
-        <v>6920029.47313406</v>
+        <v>6920029</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2441,19 +2206,9 @@
           <t>2007-07-26</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2007-07-26</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2489,15 +2244,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>104888</v>
+        <v>316141</v>
       </c>
       <c r="B17" t="n">
-        <v>73689</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2505,21 +2255,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>310</v>
+        <v>864</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2530,10 +2280,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>448545.6272013072</v>
+        <v>449540</v>
       </c>
       <c r="R17" t="n">
-        <v>6919609.857464722</v>
+        <v>6920205</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2563,19 +2313,9 @@
           <t>2007-07-26</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2007-07-26</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2611,15 +2351,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>279930</v>
+        <v>57147518</v>
       </c>
       <c r="B18" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2627,21 +2362,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>308</v>
+        <v>864</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2649,14 +2384,14 @@
       <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skorvdalen, Vemdalen,, Hjd</t>
+          <t>Skorvdalen, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>449484.3249546236</v>
+        <v>449072</v>
       </c>
       <c r="R18" t="n">
-        <v>6919996.577635235</v>
+        <v>6919618</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2683,27 +2418,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2007-07-26</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2007-07-26</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-29</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>området mellan Rönningsvallen - Gammelnipan - Nipfjället - Gråberget,</t>
+          <t>På Granlåga (3 st).  Fynd från Forskningsresan i naturvårdens utmarker 2015.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2718,31 +2443,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>malin almquist</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lars-Olof Grund</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>Lst Z Artdatabas</t>
-        </is>
-      </c>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>67081806</v>
+        <v>57147926</v>
       </c>
       <c r="B19" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2768,19 +2484,21 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kvarnsjö, Hjd</t>
+          <t>skorvdalen, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>449181.8144485008</v>
+        <v>449073</v>
       </c>
       <c r="R19" t="n">
-        <v>6919735.043600466</v>
+        <v>6919491</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2804,22 +2522,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2015-07-17</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2015-07-17</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-29</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Fynd från Forskningsresan i naturvårdens utmarker 2015.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2834,31 +2547,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>67081817</v>
+        <v>67081799</v>
       </c>
       <c r="B20" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2866,21 +2570,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1204</v>
+        <v>864</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2890,10 +2594,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>449369.6546543111</v>
+        <v>448961</v>
       </c>
       <c r="R20" t="n">
-        <v>6919905.1269934</v>
+        <v>6919446</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2923,19 +2627,9 @@
           <t>2015-07-17</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2015-07-17</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2966,15 +2660,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>67081810</v>
+        <v>67081801</v>
       </c>
       <c r="B21" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2982,21 +2671,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>864</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3006,10 +2695,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>449175.3943291654</v>
+        <v>449064</v>
       </c>
       <c r="R21" t="n">
-        <v>6919770.841866816</v>
+        <v>6919614</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3039,19 +2728,9 @@
           <t>2015-07-17</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2015-07-17</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3082,15 +2761,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>67081827</v>
+        <v>67081805</v>
       </c>
       <c r="B22" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3098,21 +2772,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>864</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3122,10 +2796,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>449112.0592677431</v>
+        <v>449064</v>
       </c>
       <c r="R22" t="n">
-        <v>6919301.176563335</v>
+        <v>6919608</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3155,19 +2829,9 @@
           <t>2015-07-17</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2015-07-17</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3198,15 +2862,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>67081805</v>
+        <v>67081806</v>
       </c>
       <c r="B23" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3238,10 +2897,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>449064.2685859642</v>
+        <v>449182</v>
       </c>
       <c r="R23" t="n">
-        <v>6919608.401119756</v>
+        <v>6919735</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3271,19 +2930,9 @@
           <t>2015-07-17</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2015-07-17</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3314,15 +2963,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>67081801</v>
+        <v>67081814</v>
       </c>
       <c r="B24" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3354,10 +2998,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>449064.3604642974</v>
+        <v>449252</v>
       </c>
       <c r="R24" t="n">
-        <v>6919614.427354066</v>
+        <v>6919861</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3387,19 +3031,9 @@
           <t>2015-07-17</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2015-07-17</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3430,15 +3064,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>67081791</v>
+        <v>67081821</v>
       </c>
       <c r="B25" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3446,21 +3075,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3470,10 +3099,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>448909.5205474578</v>
+        <v>449687</v>
       </c>
       <c r="R25" t="n">
-        <v>6919205.496284426</v>
+        <v>6920317</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3503,19 +3132,9 @@
           <t>2015-07-17</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2015-07-17</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3546,53 +3165,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>67081807</v>
+        <v>62064253</v>
       </c>
       <c r="B26" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229497</v>
+        <v>1204</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kvarnsjö, Hjd</t>
+          <t>Skorvdalen Vemdalen, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>449181.8144485008</v>
+        <v>448900</v>
       </c>
       <c r="R26" t="n">
-        <v>6919735.043600466</v>
+        <v>6918912</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3616,22 +3230,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2015-07-17</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-07-26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2015-07-17</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-07-26</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Naturinventering av Skorvdalen / Lars-Olof Grund 2007. Skorvdalen, området mellan Rönningsvallen - Gammelnipan - Nipfjället - Gråberget,</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3646,35 +3255,30 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Lars-Olof Grund</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>Lst Z Artdatabas</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>67081824</v>
+        <v>67081793</v>
       </c>
       <c r="B27" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3702,10 +3306,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>449498.9312970919</v>
+        <v>448910</v>
       </c>
       <c r="R27" t="n">
-        <v>6919887.870534043</v>
+        <v>6919205</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3735,19 +3339,9 @@
           <t>2015-07-17</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2015-07-17</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3778,37 +3372,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>67081811</v>
+        <v>67081813</v>
       </c>
       <c r="B28" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>1204</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3818,10 +3407,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>449216.8080647999</v>
+        <v>449252</v>
       </c>
       <c r="R28" t="n">
-        <v>6919807.30317061</v>
+        <v>6919861</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3851,19 +3440,9 @@
           <t>2015-07-17</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2015-07-17</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3894,37 +3473,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>67081825</v>
+        <v>67081817</v>
       </c>
       <c r="B29" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>1204</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3934,10 +3508,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>449418.5684656877</v>
+        <v>449370</v>
       </c>
       <c r="R29" t="n">
-        <v>6919731.914149977</v>
+        <v>6919905</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3967,19 +3541,9 @@
           <t>2015-07-17</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2015-07-17</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4010,37 +3574,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>67081792</v>
+        <v>67081824</v>
       </c>
       <c r="B30" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4050,10 +3609,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>448909.5205474578</v>
+        <v>449499</v>
       </c>
       <c r="R30" t="n">
-        <v>6919205.496284426</v>
+        <v>6919888</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4083,19 +3642,9 @@
           <t>2015-07-17</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2015-07-17</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4126,37 +3675,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>67081796</v>
+        <v>67081826</v>
       </c>
       <c r="B31" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>53</v>
+        <v>1204</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4166,10 +3710,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>448908.4538949762</v>
+        <v>449437</v>
       </c>
       <c r="R31" t="n">
-        <v>6919287.590229106</v>
+        <v>6919778</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4199,19 +3743,9 @@
           <t>2015-07-17</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2015-07-17</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4242,37 +3776,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>67081797</v>
+        <v>67081791</v>
       </c>
       <c r="B32" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4282,10 +3811,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>448955.8694687276</v>
+        <v>448910</v>
       </c>
       <c r="R32" t="n">
-        <v>6919321.179865071</v>
+        <v>6919205</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4315,19 +3844,9 @@
           <t>2015-07-17</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2015-07-17</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4358,15 +3877,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>67081826</v>
+        <v>67081804</v>
       </c>
       <c r="B33" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4374,21 +3888,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4398,10 +3912,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>449437.3742461529</v>
+        <v>449064</v>
       </c>
       <c r="R33" t="n">
-        <v>6919777.993725752</v>
+        <v>6919614</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4431,19 +3945,9 @@
           <t>2015-07-17</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2015-07-17</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4474,15 +3978,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>67081814</v>
+        <v>67081822</v>
       </c>
       <c r="B34" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4490,21 +3989,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>864</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4514,10 +4013,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>449251.9897558716</v>
+        <v>449560</v>
       </c>
       <c r="R34" t="n">
-        <v>6919861.477167409</v>
+        <v>6920083</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4547,19 +4046,9 @@
           <t>2015-07-17</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2015-07-17</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4593,12 +4082,7 @@
         <v>67081809</v>
       </c>
       <c r="B35" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4630,10 +4114,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>449186.9935348186</v>
+        <v>449187</v>
       </c>
       <c r="R35" t="n">
-        <v>6919800.801986065</v>
+        <v>6919801</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4663,19 +4147,9 @@
           <t>2015-07-17</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2015-07-17</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4706,53 +4180,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>67081815</v>
+        <v>437518</v>
       </c>
       <c r="B36" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79759</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>510</v>
+        <v>1778</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Fjällig knopplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Biatora fallax</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>Hepp</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kvarnsjö, Hjd</t>
+          <t>Skorvdalen, Vemdalen,, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>449251.9897558716</v>
+        <v>449628</v>
       </c>
       <c r="R36" t="n">
-        <v>6919861.477167409</v>
+        <v>6919966</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4776,22 +4245,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2015-07-17</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-07-26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2015-07-17</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-07-26</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>området mellan Rönningsvallen - Gammelnipan - Nipfjället - Gråberget,</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4806,31 +4270,26 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>malin almquist</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Lars-Olof Grund</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>Lst Z Artdatabas</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>67081799</v>
+        <v>811799</v>
       </c>
       <c r="B37" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4838,37 +4297,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>864</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kvarnsjö, Hjd</t>
+          <t>Skorvdalen, Vemdalen,, Hjd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>448960.5672012416</v>
+        <v>448546</v>
       </c>
       <c r="R37" t="n">
-        <v>6919446.306083014</v>
+        <v>6919610</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4892,22 +4353,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2015-07-17</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-07-26</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2015-07-17</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-07-26</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>området mellan Rönningsvallen - Gammelnipan - Nipfjället - Gråberget,</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4922,53 +4378,48 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>malin almquist</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Lars-Olof Grund</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>Lst Z Artdatabas</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>67081820</v>
+        <v>67081797</v>
       </c>
       <c r="B38" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>3298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4978,10 +4429,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>449560.7270706783</v>
+        <v>448956</v>
       </c>
       <c r="R38" t="n">
-        <v>6920044.565255631</v>
+        <v>6919321</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -5011,19 +4462,9 @@
           <t>2015-07-17</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2015-07-17</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5054,53 +4495,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>67081793</v>
+        <v>57147814</v>
       </c>
       <c r="B39" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Kvarnsjö, Hjd</t>
+          <t>Skorvdalen, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>448909.5205474578</v>
+        <v>449072</v>
       </c>
       <c r="R39" t="n">
-        <v>6919205.496284426</v>
+        <v>6919618</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5124,22 +4562,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2015-07-17</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-29</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2015-07-17</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-29</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På Gran. Fynd från Forskningsresan i naturvårdens utmarker 2015.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5154,53 +4587,44 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>67081822</v>
+        <v>67081790</v>
       </c>
       <c r="B40" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5210,10 +4634,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>449560.3726586823</v>
+        <v>448910</v>
       </c>
       <c r="R40" t="n">
-        <v>6920082.585752462</v>
+        <v>6919205</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5243,19 +4667,9 @@
           <t>2015-07-17</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2015-07-17</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5286,37 +4700,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>67081813</v>
+        <v>67081802</v>
       </c>
       <c r="B41" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5326,10 +4735,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>449251.9897558716</v>
+        <v>449064</v>
       </c>
       <c r="R41" t="n">
-        <v>6919861.477167409</v>
+        <v>6919614</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5359,19 +4768,9 @@
           <t>2015-07-17</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2015-07-17</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5405,16 +4804,11 @@
         <v>67081816</v>
       </c>
       <c r="B42" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -5442,10 +4836,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>449375.3162045382</v>
+        <v>449375</v>
       </c>
       <c r="R42" t="n">
-        <v>6919911.068270194</v>
+        <v>6919911</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5475,19 +4869,9 @@
           <t>2015-07-17</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2015-07-17</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5518,37 +4902,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>67081798</v>
+        <v>67081823</v>
       </c>
       <c r="B43" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5558,10 +4937,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>449013.3873224981</v>
+        <v>449567</v>
       </c>
       <c r="R43" t="n">
-        <v>6919377.800546362</v>
+        <v>6920089</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5591,19 +4970,9 @@
           <t>2015-07-17</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2015-07-17</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5634,53 +5003,50 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>67081819</v>
+        <v>57147786</v>
       </c>
       <c r="B44" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kvarnsjö, Hjd</t>
+          <t>Skorvdalen, Hjd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>449500.2049428966</v>
+        <v>449072</v>
       </c>
       <c r="R44" t="n">
-        <v>6920002.828040103</v>
+        <v>6919618</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5704,22 +5070,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2015-07-17</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-29</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2015-07-17</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-29</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På Sälg levande. Fynd från Forskningsresan i naturvårdens utmarker 2015.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5734,69 +5095,62 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>67081823</v>
+        <v>57055851</v>
       </c>
       <c r="B45" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kvarnsjö, Hjd</t>
+          <t>Skorvdalen, Hjd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>449567.440045869</v>
+        <v>449042</v>
       </c>
       <c r="R45" t="n">
-        <v>6920089.432980981</v>
+        <v>6919367</v>
       </c>
       <c r="S45" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5820,22 +5174,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2015-07-17</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-29</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2015-07-17</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-29</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På Sälg 30 cm. Fynd från Forskningsresan i naturvårdens utmarker 2015.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5850,53 +5199,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>67081804</v>
+        <v>67081798</v>
       </c>
       <c r="B46" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5906,10 +5246,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>449064.3604642974</v>
+        <v>449013</v>
       </c>
       <c r="R46" t="n">
-        <v>6919614.427354066</v>
+        <v>6919378</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5939,19 +5279,9 @@
           <t>2015-07-17</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2015-07-17</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5982,53 +5312,50 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>67081802</v>
+        <v>2090122</v>
       </c>
       <c r="B47" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83305</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6486</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kvarnsjö, Hjd</t>
+          <t>Skorvdalen, Vemdalen,, Hjd</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>449064.3604642974</v>
+        <v>448947</v>
       </c>
       <c r="R47" t="n">
-        <v>6919614.427354066</v>
+        <v>6918948</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6052,22 +5379,17 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2015-07-17</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-07-26</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2015-07-17</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-07-26</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>området mellan Rönningsvallen - Gammelnipan - Nipfjället - Gråberget,</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6082,53 +5404,48 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>malin almquist</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Lars-Olof Grund</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>Lst Z Artdatabas</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>67081803</v>
+        <v>67081819</v>
       </c>
       <c r="B48" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6138,10 +5455,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>449064.2685859642</v>
+        <v>449500</v>
       </c>
       <c r="R48" t="n">
-        <v>6919608.401119756</v>
+        <v>6920003</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6171,19 +5488,9 @@
           <t>2015-07-17</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2015-07-17</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6207,6 +5514,514 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>59520428</v>
+      </c>
+      <c r="B49" t="n">
+        <v>101897</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Skorvdalen, området mellan Rönningsvallen - Gammelnipan - Nipfjället - Gråb, Hjd</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>449064</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6919054</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2007-07-15</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2007-07-15</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Lars-Olof Grund</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>67081803</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Kvarnsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>449064</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6919608</v>
+      </c>
+      <c r="S50" t="n">
+        <v>25</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2015-07-17</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2015-07-17</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>57147755</v>
+      </c>
+      <c r="B51" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Skorvdalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>449072</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6919618</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2015-07-29</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2015-07-29</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Fynd från Forskningsresan i naturvårdens utmarker 2015.</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>57055860</v>
+      </c>
+      <c r="B52" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Skorvdalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>449042</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6919367</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2015-07-29</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2015-07-29</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>På Sälg 30 cm.  Fynd från Forskningsresan i naturvårdens utmarker 2015.</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>67081807</v>
+      </c>
+      <c r="B53" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Kvarnsjö, Hjd</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>449182</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6919735</v>
+      </c>
+      <c r="S53" t="n">
+        <v>25</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2015-07-17</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2015-07-17</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 5221-2025 artfynd.xlsx
+++ b/artfynd/A 5221-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY53"/>
+  <dimension ref="A1:AZ53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62064253</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67081793</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67081791</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67081790</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1189,6 +1214,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2090122</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1286,6 +1316,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59520428</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1387,6 +1422,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67081796</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1494,6 +1534,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104888</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1602,6 +1647,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/316127</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1710,6 +1760,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/316130</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1818,6 +1873,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/316133</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1922,6 +1982,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57147518</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2026,6 +2091,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57147926</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2127,6 +2197,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67081799</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2228,6 +2303,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67081801</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2329,6 +2409,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67081805</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2430,6 +2515,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67081804</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2538,6 +2628,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/811799</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2639,6 +2734,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67081797</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2743,6 +2843,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57147814</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2844,6 +2949,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67081802</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2948,6 +3058,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57147786</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3052,6 +3167,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57055851</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3153,6 +3273,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67081798</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3252,6 +3377,11 @@
       <c r="AY26" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67081803</t>
         </is>
       </c>
     </row>
@@ -3359,6 +3489,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57147755</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3463,6 +3598,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57055860</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3564,6 +3704,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67081811</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3665,6 +3810,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67081825</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3772,6 +3922,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81530</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3880,6 +4035,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/279930</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3981,6 +4141,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67081810</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4082,6 +4247,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67081815</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4183,6 +4353,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67081820</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4284,6 +4459,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67081827</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4392,6 +4572,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/316139</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4500,6 +4685,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/316140</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4607,6 +4797,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/316141</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4708,6 +4903,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67081806</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4809,6 +5009,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67081814</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4910,6 +5115,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67081821</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5011,6 +5221,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67081813</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5112,6 +5327,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67081817</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5213,6 +5433,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67081824</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5314,6 +5539,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67081826</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5415,6 +5645,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67081822</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5516,6 +5751,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67081809</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5622,6 +5862,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/437518</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5723,6 +5968,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67081816</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5824,6 +6074,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67081823</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5925,6 +6180,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67081819</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6026,8 +6286,67 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67081807</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>